--- a/E/SWACSP.xlsx
+++ b/E/SWACSP.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
   <si>
     <t/>
   </si>
@@ -94,13 +94,28 @@
     <t>TOLL CANDY BLUE 120G</t>
   </si>
   <si>
-    <t>20118218</t>
-  </si>
-  <si>
-    <t>IDM MSK SLIM HTM 5S</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>20143896</t>
+  </si>
+  <si>
+    <t>C/CHUP CRAZY RAFFE30</t>
+  </si>
+  <si>
+    <t>20140886</t>
+  </si>
+  <si>
+    <t>CH.CHUP BELT 1 METER</t>
+  </si>
+  <si>
+    <t>20117862</t>
+  </si>
+  <si>
+    <t>IDM MASKER PCK 5'S</t>
+  </si>
+  <si>
+    <t>20120506</t>
+  </si>
+  <si>
+    <t>IDM MASKER HIJAB 5'S</t>
   </si>
 </sst>
 </file>
@@ -493,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -694,13 +709,73 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
